--- a/Result/profitability/4767.xlsx
+++ b/Result/profitability/4767.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM40"/>
+  <dimension ref="A1:AM41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5510,6 +5510,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4767</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>229</v>
+      </c>
+      <c r="D41" t="n">
+        <v>151</v>
+      </c>
+      <c r="E41" t="n">
+        <v>77</v>
+      </c>
+      <c r="F41" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="G41" t="n">
+        <v>35</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>15.21%</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>3</v>
+      </c>
+      <c r="J41" t="n">
+        <v>38</v>
+      </c>
+      <c r="K41" t="n">
+        <v>34</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.5225</v>
+      </c>
+      <c r="N41" t="n">
+        <v>24.8425</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.8620689655172415</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>6.479999999999997</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.2375366568914954</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>-16.42857142857143</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.5493345571363011</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK41" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
